--- a/consulting_forms/033_market_entry_research_consulting_contact_form--consulting_forms.xlsx
+++ b/consulting_forms/033_market_entry_research_consulting_contact_form--consulting_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'not_started'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Not Started'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'image'}</t>
+          <t>image</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Image'}</t>
+          <t>Image</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'document'}</t>
+          <t>document</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Document'}</t>
+          <t>Document</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'video'}</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Video'}</t>
+          <t>Video</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Small'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Large'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'pdf'}</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'PDF'}</t>
+          <t>PDF</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'docx'}</t>
+          <t>docx</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'DOCX'}</t>
+          <t>DOCX</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'csv'}</t>
+          <t>csv</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'CSV'}</t>
+          <t>CSV</t>
         </is>
       </c>
     </row>
